--- a/backend/output/template/公共接口模板.xlsx
+++ b/backend/output/template/公共接口模板.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/KeenRunner/backend/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AC58226-2267-B944-85A9-AB42F7F4FEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05890134-64E9-EF43-BDF9-C552255029D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="58300" yWindow="5760" windowWidth="28360" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="模板" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="帮助" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>

--- a/backend/output/template/公共接口模板.xlsx
+++ b/backend/output/template/公共接口模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/Fastapi-Vue/KeenRunner/backend/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05890134-64E9-EF43-BDF9-C552255029D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E88CA4-DBB9-644C-A5A6-05705E69ABDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58300" yWindow="5760" windowWidth="28360" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40960" yWindow="1740" windowWidth="36380" windowHeight="24240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -357,7 +357,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
